--- a/pacjenci/ANNA BĄK.xlsx
+++ b/pacjenci/ANNA BĄK.xlsx
@@ -485,12 +485,12 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -529,7 +529,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -573,7 +573,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -617,12 +617,12 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -630,17 +630,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/ANNA BĄK.xlsx
+++ b/pacjenci/ANNA BĄK.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>23.11.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak grudkowy G1. Progresja FL?  .</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 56 min od podania 18F-FDG. Glikemia: 90 mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Wzmożony metabolizm FDG na tylnej ścianie nosogardła SUV max do 10,9- do kontroli laryngologicznej. Aktywne metabolicznie drobne węzły chłonne szyjne grupy 2B wielkości do 7 mm SUV max do 3,6 Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie węzeł chłonny podobojczykowy lewy wielkości 12 mm SUV max 5,1. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Bardzo liczne, aktywne metabolicznie obszary w śledzionie wielkości do 30x30x31 mm wg PET SUV max do 13,8 [Im fuz. 142]. Aktywne metabolicznie obszary w lewym płacie wątroby wielkości do 18 mm wg PET SUV max do 6,4. Aktywny metabolicznie węzeł chłonne pachwinowe prawe wielkości do 18 mm SUV max 17,6. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii  Układ kostny: Bardzo liczne, aktywne metabolicznie obszary w całym układzie kostnym objętym badaniem wielkości największe: - na poziomie Th4 wielkości 36x29x35 mm wg PET SUV max do 19,0  [Im fuz. 97] - w masywie bocznym lewym kości krzyżowej wielkości do 20x60x33 mm wg PET SUV max do 21,4 [Im fuz. 221] - w talerzu kości biodrowej prawej wielkości 16x35mm wg PET SUV max do 16,3  Wartości referencyjne: MBPS SUVmax Prawy płat wątroby SUVmax do 3,1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z masywnym zajęciem układu kostnego, śledziony, wątroby oraz pojedynczych węzłów chłonnych po obu stronach przepony.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>21.4</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>17.05.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak grudkowy G1. Ocena remisji choroby po 4 cyklach immunochemioterapii.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 63 min od podania 18F-FDG. Glikemia: 95 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Wydatne zwapnienia w topografii sierpu mózgu. Drobne polipowate zgrubienia błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Tarczyca powiększona, o nieco niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne śródpiersiowe wielkości do 10x8mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowe kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykregowych i w stawach żebrowo-poprzecznych. Wydatna wyspa kostna w trzonie prawej kości biodrowej oraz w masywie bocznym kości krzyżowej po stronie lewej . Poza tym drobne wyspy kostne w kościach udowych i w kościach miednicy.  Wartości referencyjne: MBPS SUVmax do 1,4; Prawy płat wątroby SUVmax do 1,9.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź procesu chłoniakowego na stosowane leczenie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1.9</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>15.09.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak grudkowy G1. Ocena remisji choroby po 8 cyklach immunochemioterapii.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 63 min od podania 18F-FDG. Glikemia: 96 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Wydatne zwapnienia w topografii sierpu mózgu. Drobne polipowate zgrubienia błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Tarczyca powiększona, o nieco niejednorodnym cieniowaniu w przeglądowym badaniu TK - opisywana już poprzednio..  Klatka piersiowa i śródpiersie: Zagęszczenia miąższowe w segmencie 6 i oraz obwodowo w segmentach 8,9 i 10 płuca lewego, SUV max do 3,5- do oceny z całością obrazu klinicznego.  Pobudzenie metaboliczne w segm 6 płuca prawego na obszaru zageszczeń wielkości 11mm, SUV max 4,0. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne śródpiersiowe wielkości do 10x8mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe.  Układ kostny: Zmiany zwyrodnieniowe kręgosłupa odcinkowo z pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykregowych i w stawach żebrowo-poprzecznych. Wydatna wyspa kostna w trzonie prawej kości biodrowej oraz w masywie bocznym kości krzyżowej po stronie lewej . Poza tym drobne wyspy kostne w kościach udowych i w kościach miednicy.  Wartości referencyjne: MBPS SUVmax do 2,7 Prawy płat wątroby SUVmax do 3,3.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono zmiany w płucach - do oceny z całością obrazu klinicznego. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>4</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>19.09.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak grudkowy G1. Ocena remisji choroby po 8 cyklach immunochemioterapii.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 95 mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Wydatne zwapnienia w topografii sierpu mózgu. Tarczyca powiększona, o nieco niejednorodnym cieniowaniu w przeglądowym badaniu TK - opisywana już poprzednio..  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne śródpiersiowe wielkości do 9x7mm. Niewielkie obszary o typie mlecznej szyby w topografii podstawnej części segm. 3 płuca lewego. Niewielkie zmiany miąższowo-włókniste w segm. 3/4 płuca lewego [SUV max do 2,5]. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe.  Układ kostny: Zmiany zwyrodnieniowe kręgosłupa odcinkowo z pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Wydatna wyspa kostna w trzonie prawej kości biodrowej oraz w masywie bocznym kości krzyżowej po stronie lewej . Poza tym drobne wyspy kostne w kościach udowych i w kościach miednicy.  Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 3,0.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu chłoniakowego. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>3</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/ANNA BĄK.xlsx
+++ b/pacjenci/ANNA BĄK.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 56 min od podania 18F-FDG. Glikemia: 90 mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Wzmożony metabolizm FDG na tylnej ścianie nosogardła SUV max do 10,9- do kontroli laryngologicznej. Aktywne metabolicznie drobne węzły chłonne szyjne grupy 2B wielkości do 7 mm SUV max do 3,6 Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie węzeł chłonny podobojczykowy lewy wielkości 12 mm SUV max 5,1. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Bardzo liczne, aktywne metabolicznie obszary w śledzionie wielkości do 30x30x31 mm wg PET SUV max do 13,8 [Im fuz. 142]. Aktywne metabolicznie obszary w lewym płacie wątroby wielkości do 18 mm wg PET SUV max do 6,4. Aktywny metabolicznie węzeł chłonne pachwinowe prawe wielkości do 18 mm SUV max 17,6. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii  Układ kostny: Bardzo liczne, aktywne metabolicznie obszary w całym układzie kostnym objętym badaniem wielkości największe: - na poziomie Th4 wielkości 36x29x35 mm wg PET SUV max do 19,0  [Im fuz. 97] - w masywie bocznym lewym kości krzyżowej wielkości do 20x60x33 mm wg PET SUV max do 21,4 [Im fuz. 221] - w talerzu kości biodrowej prawej wielkości 16x35mm wg PET SUV max do 16,3  Wartości referencyjne: MBPS SUVmax Prawy płat wątroby SUVmax do 3,1</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG na tylnej ścianie nosogardła SUV max do 10,9- do kontroli laryngologicznej. Aktywne metabolicznie drobne węzły chłonne szyjne grupy 2B wielkości do 7 mm SUV max do 3,6 Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie węzeł chłonny podobojczykowy lewy wielkości 12 mm SUV max 5,1. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Bardzo liczne, aktywne metabolicznie obszary w śledzionie wielkości do 30x30x31 mm wg PET SUV max do 13,8 [Im fuz. 142]. Aktywne metabolicznie obszary w lewym płacie wątroby wielkości do 18 mm wg PET SUV max do 6,4. Aktywny metabolicznie węzeł chłonne pachwinowe prawe wielkości do 18 mm SUV max 17,6. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Bardzo liczne, aktywne metabolicznie obszary w całym układzie kostnym objętym badaniem wielkości największe: - na poziomie Th4 wielkości 36x29x35 mm wg PET SUV max do 19,0  [Im fuz. 97] - w masywie bocznym lewym kości krzyżowej wielkości do 20x60x33 mm wg PET SUV max do 21,4 [Im fuz. 221] - w talerzu kości biodrowej prawej wielkości 16x35mm wg PET SUV max do 16,3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z masywnym zajęciem układu kostnego, śledziony, wątroby oraz pojedynczych węzłów chłonnych po obu stronach przepony.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>21.4</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 63 min od podania 18F-FDG. Glikemia: 95 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Wydatne zwapnienia w topografii sierpu mózgu. Drobne polipowate zgrubienia błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Tarczyca powiększona, o nieco niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne śródpiersiowe wielkości do 10x8mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowe kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykregowych i w stawach żebrowo-poprzecznych. Wydatna wyspa kostna w trzonie prawej kości biodrowej oraz w masywie bocznym kości krzyżowej po stronie lewej . Poza tym drobne wyspy kostne w kościach udowych i w kościach miednicy.  Wartości referencyjne: MBPS SUVmax do 1,4; Prawy płat wątroby SUVmax do 1,9.</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Wydatne zwapnienia w topografii sierpu mózgu. Drobne polipowate zgrubienia błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Tarczyca powiększona, o nieco niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne śródpiersiowe wielkości do 10x8mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowe kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykregowych i w stawach żebrowo-poprzecznych. Wydatna wyspa kostna w trzonie prawej kości biodrowej oraz w masywie bocznym kości krzyżowej po stronie lewej . Poza tym drobne wyspy kostne w kościach udowych i w kościach miednicy.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź procesu chłoniakowego na stosowane leczenie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>1.9</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 63 min od podania 18F-FDG. Glikemia: 96 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Wydatne zwapnienia w topografii sierpu mózgu. Drobne polipowate zgrubienia błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Tarczyca powiększona, o nieco niejednorodnym cieniowaniu w przeglądowym badaniu TK - opisywana już poprzednio..  Klatka piersiowa i śródpiersie: Zagęszczenia miąższowe w segmencie 6 i oraz obwodowo w segmentach 8,9 i 10 płuca lewego, SUV max do 3,5- do oceny z całością obrazu klinicznego.  Pobudzenie metaboliczne w segm 6 płuca prawego na obszaru zageszczeń wielkości 11mm, SUV max 4,0. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne śródpiersiowe wielkości do 10x8mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe.  Układ kostny: Zmiany zwyrodnieniowe kręgosłupa odcinkowo z pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykregowych i w stawach żebrowo-poprzecznych. Wydatna wyspa kostna w trzonie prawej kości biodrowej oraz w masywie bocznym kości krzyżowej po stronie lewej . Poza tym drobne wyspy kostne w kościach udowych i w kościach miednicy.  Wartości referencyjne: MBPS SUVmax do 2,7 Prawy płat wątroby SUVmax do 3,3.</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Wydatne zwapnienia w topografii sierpu mózgu. Drobne polipowate zgrubienia błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej. Tarczyca powiększona, o nieco niejednorodnym cieniowaniu w przeglądowym badaniu TK - opisywana już poprzednio..</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Zagęszczenia miąższowe w segmencie 6 i oraz obwodowo w segmentach 8,9 i 10 płuca lewego, SUV max do 3,5- do oceny z całością obrazu klinicznego.  Pobudzenie metaboliczne w segm 6 płuca prawego na obszaru zageszczeń wielkości 11mm, SUV max 4,0. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne śródpiersiowe wielkości do 10x8mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Zmiany zwyrodnieniowe kręgosłupa odcinkowo z pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykregowych i w stawach żebrowo-poprzecznych. Wydatna wyspa kostna w trzonie prawej kości biodrowej oraz w masywie bocznym kości krzyżowej po stronie lewej . Poza tym drobne wyspy kostne w kościach udowych i w kościach miednicy.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono zmiany w płucach - do oceny z całością obrazu klinicznego. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 95 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Wydatne zwapnienia w topografii sierpu mózgu. Tarczyca powiększona, o nieco niejednorodnym cieniowaniu w przeglądowym badaniu TK - opisywana już poprzednio..  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne śródpiersiowe wielkości do 9x7mm. Niewielkie obszary o typie mlecznej szyby w topografii podstawnej części segm. 3 płuca lewego. Niewielkie zmiany miąższowo-włókniste w segm. 3/4 płuca lewego [SUV max do 2,5]. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe.  Układ kostny: Zmiany zwyrodnieniowe kręgosłupa odcinkowo z pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Wydatna wyspa kostna w trzonie prawej kości biodrowej oraz w masywie bocznym kości krzyżowej po stronie lewej . Poza tym drobne wyspy kostne w kościach udowych i w kościach miednicy.  Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 3,0.</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Wydatne zwapnienia w topografii sierpu mózgu. Tarczyca powiększona, o nieco niejednorodnym cieniowaniu w przeglądowym badaniu TK - opisywana już poprzednio..</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne śródpiersiowe wielkości do 9x7mm. Niewielkie obszary o typie mlecznej szyby w topografii podstawnej części segm. 3 płuca lewego. Niewielkie zmiany miąższowo-włókniste w segm. 3/4 płuca lewego [SUV max do 2,5]. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Stan po cholecystektomii - w loży widoczne są klipsy naczyniowe.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Zmiany zwyrodnieniowe kręgosłupa odcinkowo z pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Wielopoziomowo guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Zmiany wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Wydatna wyspa kostna w trzonie prawej kości biodrowej oraz w masywie bocznym kości krzyżowej po stronie lewej . Poza tym drobne wyspy kostne w kościach udowych i w kościach miednicy.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu chłoniakowego. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>3</v>
       </c>
     </row>
